--- a/output/daily_screen_20260618.xlsx
+++ b/output/daily_screen_20260618.xlsx
@@ -703,7 +703,7 @@
         <v>1080</v>
       </c>
       <c r="R2" t="n">
-        <v>93330100</v>
+        <v>90546467</v>
       </c>
       <c r="S2" t="n">
         <v>961.8</v>
@@ -739,13 +739,13 @@
         <v>3.29940411186986</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.7784493248050468</v>
+        <v>0.7553215032965073</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.879427055754038</v>
+        <v>2.931721180709148</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2.100977730948991</v>
+        <v>-2.176399677412641</v>
       </c>
       <c r="AG2" t="n">
         <v>100</v>
@@ -845,7 +845,7 @@
         <v>1835</v>
       </c>
       <c r="R3" t="n">
-        <v>3847667</v>
+        <v>3466139</v>
       </c>
       <c r="S3" t="n">
         <v>1623</v>
@@ -881,13 +881,13 @@
         <v>2.438061772183397</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.2616953941913094</v>
+        <v>0.2385675726827698</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.018084716067575</v>
+        <v>2.070378841022684</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1.756389321876265</v>
+        <v>-1.831811268339914</v>
       </c>
       <c r="AG3" t="n">
         <v>90</v>
@@ -987,7 +987,7 @@
         <v>145.5</v>
       </c>
       <c r="R4" t="n">
-        <v>295448011</v>
+        <v>293666572</v>
       </c>
       <c r="S4" t="n">
         <v>140.3</v>
@@ -1023,13 +1023,13 @@
         <v>1.566137531608332</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1311000786415373</v>
+        <v>0.1079722571329977</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.14616047549251</v>
+        <v>1.19845460044762</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1.015060396850973</v>
+        <v>-1.090482343314622</v>
       </c>
       <c r="AG4" t="n">
         <v>84</v>
@@ -1129,7 +1129,7 @@
         <v>613</v>
       </c>
       <c r="R5" t="n">
-        <v>35566469</v>
+        <v>34220952</v>
       </c>
       <c r="S5" t="n">
         <v>596</v>
@@ -1147,13 +1147,13 @@
         <v>9.449331750271995</v>
       </c>
       <c r="X5" t="n">
-        <v>8.063435943982336</v>
+        <v>8.063435943982334</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.385895806289659</v>
+        <v>1.38589580628966</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.9674473519951619</v>
+        <v>-0.9674473519951601</v>
       </c>
       <c r="AA5" t="b">
         <v>1</v>
@@ -1165,13 +1165,13 @@
         <v>0.8603945371775417</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.07875051812767642</v>
+        <v>0.05562269661913688</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.4404174810617192</v>
+        <v>0.4927116060168291</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.3616669629340428</v>
+        <v>-0.4370889093976922</v>
       </c>
       <c r="AG5" t="n">
         <v>76</v>
@@ -1271,7 +1271,7 @@
         <v>1110</v>
       </c>
       <c r="R6" t="n">
-        <v>11715655</v>
+        <v>11451045</v>
       </c>
       <c r="S6" t="n">
         <v>1013.8</v>
@@ -1289,13 +1289,13 @@
         <v>68.9095567301747</v>
       </c>
       <c r="X6" t="n">
-        <v>40.17057783521094</v>
+        <v>40.17057783521093</v>
       </c>
       <c r="Y6" t="n">
-        <v>28.73897889496376</v>
+        <v>28.73897889496377</v>
       </c>
       <c r="Z6" t="n">
-        <v>23.63985513649801</v>
+        <v>23.63985513649803</v>
       </c>
       <c r="AA6" t="b">
         <v>1</v>
@@ -1307,13 +1307,13 @@
         <v>1.514156285390714</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.4602419449409125</v>
+        <v>0.437114123432373</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.094179229274891</v>
+        <v>1.146473354230001</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.6339372843339786</v>
+        <v>-0.709359230797628</v>
       </c>
       <c r="AG6" t="n">
         <v>98</v>
@@ -1413,7 +1413,7 @@
         <v>5195</v>
       </c>
       <c r="R7" t="n">
-        <v>2971148</v>
+        <v>2793257</v>
       </c>
       <c r="S7" t="n">
         <v>4728</v>
@@ -1449,13 +1449,13 @@
         <v>1.324384787472036</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.3782348205191532</v>
+        <v>0.3551069990106137</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.9044077313562133</v>
+        <v>0.9567018563113232</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.5261729108370601</v>
+        <v>-0.6015948573007095</v>
       </c>
       <c r="AG7" t="n">
         <v>96</v>
@@ -1555,7 +1555,7 @@
         <v>700</v>
       </c>
       <c r="R8" t="n">
-        <v>5434900</v>
+        <v>5083688</v>
       </c>
       <c r="S8" t="n">
         <v>634</v>
@@ -1576,10 +1576,10 @@
         <v>28.45490455737531</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.100745244828929</v>
+        <v>5.100745244828936</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.269599205740235</v>
+        <v>-1.269599205740228</v>
       </c>
       <c r="AA8" t="b">
         <v>1</v>
@@ -1591,13 +1591,13 @@
         <v>2.146067415730337</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.2824122237737903</v>
+        <v>0.2592844022652507</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.726090359614515</v>
+        <v>1.778384484569625</v>
       </c>
       <c r="AF8" t="n">
-        <v>-1.443678135840724</v>
+        <v>-1.519100082304374</v>
       </c>
       <c r="AG8" t="n">
         <v>92</v>
@@ -1697,7 +1697,7 @@
         <v>1590</v>
       </c>
       <c r="R9" t="n">
-        <v>5945272</v>
+        <v>5844151</v>
       </c>
       <c r="S9" t="n">
         <v>1377</v>
@@ -1715,13 +1715,13 @@
         <v>98.015285816085</v>
       </c>
       <c r="X9" t="n">
-        <v>47.87158866416893</v>
+        <v>47.87158866416891</v>
       </c>
       <c r="Y9" t="n">
-        <v>50.14369715191607</v>
+        <v>50.14369715191609</v>
       </c>
       <c r="Z9" t="n">
-        <v>37.83645712940327</v>
+        <v>37.83645712940329</v>
       </c>
       <c r="AA9" t="b">
         <v>1</v>
@@ -1733,13 +1733,13 @@
         <v>0.9495338282124184</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.3697474802928242</v>
+        <v>0.3466196587842847</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.5295567720965959</v>
+        <v>0.5818508970517058</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.1598092918037717</v>
+        <v>-0.2352312382674211</v>
       </c>
       <c r="AG9" t="n">
         <v>94</v>
@@ -1839,7 +1839,7 @@
         <v>642</v>
       </c>
       <c r="R10" t="n">
-        <v>52841590</v>
+        <v>52039171</v>
       </c>
       <c r="S10" t="n">
         <v>609.4</v>
@@ -1875,13 +1875,13 @@
         <v>2.215862658556076</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.2535487912800234</v>
+        <v>0.2304209697714839</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.795885602440253</v>
+        <v>1.848179727395363</v>
       </c>
       <c r="AF10" t="n">
-        <v>-1.54233681116023</v>
+        <v>-1.617758757623879</v>
       </c>
       <c r="AG10" t="n">
         <v>88</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>79.8</v>
+        <v>80</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>2410</v>
       </c>
       <c r="R11" t="n">
-        <v>48317253</v>
+        <v>46429815</v>
       </c>
       <c r="S11" t="n">
         <v>2376</v>
@@ -1996,16 +1996,16 @@
         <v>2159.367419433594</v>
       </c>
       <c r="W11" t="n">
-        <v>28.72707528692808</v>
+        <v>28.72707528479623</v>
       </c>
       <c r="X11" t="n">
-        <v>22.60670966297884</v>
+        <v>22.60670965872987</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.12036562394924</v>
+        <v>6.120365626066363</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.263885528615337</v>
+        <v>3.263885530995257</v>
       </c>
       <c r="AA11" t="b">
         <v>1</v>
@@ -2017,19 +2017,19 @@
         <v>0.3350439016104065</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.03960952781443594</v>
+        <v>-0.06273734932297548</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.08493315450541594</v>
+        <v>-0.03263902955030606</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.04532362669098</v>
+        <v>-0.03009831977266941</v>
       </c>
       <c r="AG11" t="n">
         <v>57.99999999999999</v>
       </c>
       <c r="AH11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI11" t="b">
         <v>1</v>
@@ -2123,7 +2123,7 @@
         <v>5600</v>
       </c>
       <c r="R12" t="n">
-        <v>1904716</v>
+        <v>1607030</v>
       </c>
       <c r="S12" t="n">
         <v>5156</v>
@@ -2141,13 +2141,13 @@
         <v>121.2452213367114</v>
       </c>
       <c r="X12" t="n">
-        <v>70.43235211848061</v>
+        <v>70.43235211848045</v>
       </c>
       <c r="Y12" t="n">
-        <v>50.81286921823083</v>
+        <v>50.81286921823099</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.766482249075558</v>
+        <v>8.766482249075764</v>
       </c>
       <c r="AA12" t="b">
         <v>1</v>
@@ -2159,13 +2159,13 @@
         <v>1.003577817531306</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.07081958456021953</v>
+        <v>0.04769176305167999</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.5836007614154832</v>
+        <v>0.6358948863705931</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.5127811768552637</v>
+        <v>-0.5882031233189131</v>
       </c>
       <c r="AG12" t="n">
         <v>74</v>
@@ -2265,7 +2265,7 @@
         <v>232.5</v>
       </c>
       <c r="R13" t="n">
-        <v>14276665</v>
+        <v>13928151</v>
       </c>
       <c r="S13" t="n">
         <v>223.9</v>
@@ -2283,13 +2283,13 @@
         <v>0.1808336102083388</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03026743330141782</v>
+        <v>0.03026743330140001</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.150566176906921</v>
+        <v>0.1505661769069388</v>
       </c>
       <c r="Z13" t="n">
-        <v>-1.391634437305882</v>
+        <v>-1.391634437305859</v>
       </c>
       <c r="AA13" t="b">
         <v>1</v>
@@ -2301,13 +2301,13 @@
         <v>0.603448275862069</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.06156643056961064</v>
+        <v>-0.08469425207815018</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.1834712197462465</v>
+        <v>0.2357653447013563</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.2450376503158571</v>
+        <v>-0.3204595967795065</v>
       </c>
       <c r="AG13" t="n">
         <v>44</v>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>78.19999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>308.5</v>
       </c>
       <c r="R14" t="n">
-        <v>52208586</v>
+        <v>51061461</v>
       </c>
       <c r="S14" t="n">
         <v>286</v>
@@ -2443,19 +2443,19 @@
         <v>0.07867132867132876</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.04453893751472027</v>
+        <v>-0.0676667590232598</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.3413057274444937</v>
+        <v>-0.2890116024893838</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.2967667899297735</v>
+        <v>0.221344843466124</v>
       </c>
       <c r="AG14" t="n">
         <v>56.00000000000001</v>
       </c>
       <c r="AH14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI14" t="b">
         <v>1</v>
@@ -2549,7 +2549,7 @@
         <v>18960</v>
       </c>
       <c r="R15" t="n">
-        <v>174612</v>
+        <v>149137</v>
       </c>
       <c r="S15" t="n">
         <v>18371</v>
@@ -2567,13 +2567,13 @@
         <v>289.021056815247</v>
       </c>
       <c r="X15" t="n">
-        <v>214.9283984995496</v>
+        <v>214.9283984995492</v>
       </c>
       <c r="Y15" t="n">
-        <v>74.09265831569741</v>
+        <v>74.09265831569778</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.48409714335804</v>
+        <v>10.48409714335853</v>
       </c>
       <c r="AA15" t="b">
         <v>1</v>
@@ -2585,13 +2585,13 @@
         <v>0.6537287396423899</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.03007440534679762</v>
+        <v>0.00694658383825808</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.2337516835265674</v>
+        <v>0.2860458084816773</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.2036772781797698</v>
+        <v>-0.2790992246434192</v>
       </c>
       <c r="AG15" t="n">
         <v>68</v>
@@ -2691,7 +2691,7 @@
         <v>1235</v>
       </c>
       <c r="R16" t="n">
-        <v>1901137</v>
+        <v>1705572</v>
       </c>
       <c r="S16" t="n">
         <v>1149</v>
@@ -2709,13 +2709,13 @@
         <v>15.31122248434031</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.758222819219924</v>
+        <v>-3.758222819220004</v>
       </c>
       <c r="Y16" t="n">
-        <v>19.06944530356023</v>
+        <v>19.06944530356031</v>
       </c>
       <c r="Z16" t="n">
-        <v>10.78046809642058</v>
+        <v>10.78046809642068</v>
       </c>
       <c r="AA16" t="b">
         <v>1</v>
@@ -2727,13 +2727,13 @@
         <v>0.4879518072289157</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.009817256749730774</v>
+        <v>-0.01331056475880876</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.06797475111309326</v>
+        <v>0.1202688760682031</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.05815749436336248</v>
+        <v>-0.1335794408270119</v>
       </c>
       <c r="AG16" t="n">
         <v>62</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>71.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>3965</v>
       </c>
       <c r="R17" t="n">
-        <v>1997604</v>
+        <v>1871730</v>
       </c>
       <c r="S17" t="n">
         <v>3853</v>
@@ -2851,13 +2851,13 @@
         <v>39.06539743496523</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.118622287748748</v>
+        <v>-2.118622287748835</v>
       </c>
       <c r="Y17" t="n">
-        <v>41.18401972271398</v>
+        <v>41.18401972271407</v>
       </c>
       <c r="Z17" t="n">
-        <v>37.57305462714218</v>
+        <v>37.5730546271423</v>
       </c>
       <c r="AA17" t="b">
         <v>1</v>
@@ -2869,19 +2869,19 @@
         <v>0.02987012987012982</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.06748042450464165</v>
+        <v>0.04435260299610211</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.3901069262456927</v>
+        <v>-0.3378128012905828</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.4575873507503343</v>
+        <v>0.3821654042866849</v>
       </c>
       <c r="AG17" t="n">
         <v>70</v>
       </c>
       <c r="AH17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI17" t="b">
         <v>1</v>
@@ -2975,7 +2975,7 @@
         <v>174.5</v>
       </c>
       <c r="R18" t="n">
-        <v>17141419</v>
+        <v>16947495</v>
       </c>
       <c r="S18" t="n">
         <v>171.3</v>
@@ -2999,7 +2999,7 @@
         <v>0.9637640155962179</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.5056640413214175</v>
+        <v>0.5056640413214177</v>
       </c>
       <c r="AA18" t="b">
         <v>1</v>
@@ -3011,13 +3011,13 @@
         <v>0.5442477876106195</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.05593197872427536</v>
+        <v>-0.07905980023281489</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.1242707314947971</v>
+        <v>0.1765648564499069</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.1802027102190724</v>
+        <v>-0.2556246566827218</v>
       </c>
       <c r="AG18" t="n">
         <v>48</v>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>66.60000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>3610</v>
       </c>
       <c r="R19" t="n">
-        <v>392583</v>
+        <v>369274</v>
       </c>
       <c r="S19" t="n">
         <v>3571</v>
@@ -3135,13 +3135,13 @@
         <v>36.41058042260102</v>
       </c>
       <c r="X19" t="n">
-        <v>-4.263569779695589</v>
+        <v>-4.263569779695644</v>
       </c>
       <c r="Y19" t="n">
-        <v>40.6741502022966</v>
+        <v>40.67415020229666</v>
       </c>
       <c r="Z19" t="n">
-        <v>39.22918240294742</v>
+        <v>39.22918240294748</v>
       </c>
       <c r="AA19" t="b">
         <v>1</v>
@@ -3153,19 +3153,19 @@
         <v>0.05865102639296182</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.04559832588754165</v>
+        <v>-0.06872614739608118</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.3613260297228607</v>
+        <v>-0.3090319047677508</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.315727703835319</v>
+        <v>0.2403057573716696</v>
       </c>
       <c r="AG19" t="n">
         <v>54</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI19" t="b">
         <v>1</v>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>62.8</v>
+        <v>63</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>100.5</v>
       </c>
       <c r="R20" t="n">
-        <v>5792966</v>
+        <v>5752558</v>
       </c>
       <c r="S20" t="n">
         <v>99.56000061035157</v>
@@ -3274,16 +3274,16 @@
         <v>97.92833366394044</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8774655556775883</v>
+        <v>0.8774655556775741</v>
       </c>
       <c r="X20" t="n">
-        <v>0.2303048802258596</v>
+        <v>0.2303048802258391</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.6471606754517287</v>
+        <v>0.6471606754517351</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.6278660250203199</v>
+        <v>0.6278660250203277</v>
       </c>
       <c r="AA20" t="b">
         <v>1</v>
@@ -3295,19 +3295,19 @@
         <v>0.08297410231708313</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.0708542452436407</v>
+        <v>-0.09398206675218024</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.3370029537987393</v>
+        <v>-0.2847088288436295</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.2661487085550986</v>
+        <v>0.1907267620914492</v>
       </c>
       <c r="AG20" t="n">
         <v>40</v>
       </c>
       <c r="AH20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI20" t="b">
         <v>1</v>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>61.2</v>
+        <v>61.4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>19.10000038146973</v>
       </c>
       <c r="R21" t="n">
-        <v>382092503</v>
+        <v>382434690</v>
       </c>
       <c r="S21" t="n">
         <v>18.87999992370606</v>
@@ -3419,13 +3419,13 @@
         <v>-0.001849338577535775</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.002493650800728089</v>
+        <v>-0.002493650800728161</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.0006443122231923138</v>
+        <v>0.0006443122231923858</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.03545533046064332</v>
+        <v>-0.03545533046064323</v>
       </c>
       <c r="AA21" t="b">
         <v>1</v>
@@ -3437,19 +3437,19 @@
         <v>0.002624732095101834</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.07375973976832828</v>
+        <v>-0.09688756127686782</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.4173523240207206</v>
+        <v>-0.3650581990656108</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.3435925842523924</v>
+        <v>0.2681706377887429</v>
       </c>
       <c r="AG21" t="n">
         <v>38</v>
       </c>
       <c r="AH21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI21" t="b">
         <v>1</v>
@@ -3543,7 +3543,7 @@
         <v>104</v>
       </c>
       <c r="R22" t="n">
-        <v>73198901</v>
+        <v>72390881</v>
       </c>
       <c r="S22" t="n">
         <v>97.28000030517578</v>
@@ -3561,13 +3561,13 @@
         <v>2.192850877210518</v>
       </c>
       <c r="X22" t="n">
-        <v>2.256292561874765</v>
+        <v>2.256292561874762</v>
       </c>
       <c r="Y22" t="n">
-        <v>-0.0634416846642476</v>
+        <v>-0.06344168466424449</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.9254176202801014</v>
+        <v>-0.9254176202800979</v>
       </c>
       <c r="AA22" t="b">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0.7838765242022261</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.247013685186865</v>
+        <v>0.2238858636783254</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.3638994680864036</v>
+        <v>0.4161935930415135</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.1168857828995387</v>
+        <v>-0.1923077293631881</v>
       </c>
       <c r="AG22" t="n">
         <v>86</v>
@@ -3683,7 +3683,7 @@
         <v>242.5</v>
       </c>
       <c r="R23" t="n">
-        <v>9094925</v>
+        <v>8909870</v>
       </c>
       <c r="S23" t="n">
         <v>234.9</v>
@@ -3701,13 +3701,13 @@
         <v>3.705876277978376</v>
       </c>
       <c r="X23" t="n">
-        <v>5.720424743544816</v>
+        <v>5.720424743544778</v>
       </c>
       <c r="Y23" t="n">
-        <v>-2.01454846556644</v>
+        <v>-2.014548465566402</v>
       </c>
       <c r="Z23" t="n">
-        <v>-3.58913594957022</v>
+        <v>-3.5891359495702</v>
       </c>
       <c r="AA23" t="b">
         <v>1</v>
@@ -3719,13 +3719,13 @@
         <v>0.6819836647615274</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.06887525113996151</v>
+        <v>0.04574742963142198</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.2620066086457049</v>
+        <v>0.3143007336008148</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.1931313575057434</v>
+        <v>-0.2685533039693928</v>
       </c>
       <c r="AG23" t="n">
         <v>72</v>
@@ -3823,7 +3823,7 @@
         <v>160</v>
       </c>
       <c r="R24" t="n">
-        <v>11946175</v>
+        <v>11662345</v>
       </c>
       <c r="S24" t="n">
         <v>146.6</v>
@@ -3841,13 +3841,13 @@
         <v>2.80391623660816</v>
       </c>
       <c r="X24" t="n">
-        <v>3.644859539006668</v>
+        <v>3.644859539006667</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.8409433023985087</v>
+        <v>-0.8409433023985069</v>
       </c>
       <c r="Z24" t="n">
-        <v>-2.68454642839988</v>
+        <v>-2.684546428399878</v>
       </c>
       <c r="AA24" t="b">
         <v>1</v>
@@ -3859,13 +3859,13 @@
         <v>0.7710085546940613</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.08433690362527169</v>
+        <v>0.06120908211673215</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.3510314985782388</v>
+        <v>0.4033256235333487</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.2666945949529671</v>
+        <v>-0.3421165414166165</v>
       </c>
       <c r="AG24" t="n">
         <v>78</v>
@@ -3963,7 +3963,7 @@
         <v>252</v>
       </c>
       <c r="R25" t="n">
-        <v>26294690</v>
+        <v>25915908</v>
       </c>
       <c r="S25" t="n">
         <v>231.8113830566406</v>
@@ -3999,13 +3999,13 @@
         <v>2.974146383428255</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.02348721779775031</v>
+        <v>0.0003593962892107783</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.554169327312432</v>
+        <v>2.606463452267542</v>
       </c>
       <c r="AF25" t="n">
-        <v>-2.530682109514682</v>
+        <v>-2.606104055978332</v>
       </c>
       <c r="AG25" t="n">
         <v>66</v>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>376</v>
       </c>
       <c r="R26" t="n">
-        <v>22484821</v>
+        <v>22067558</v>
       </c>
       <c r="S26" t="n">
         <v>370.9</v>
@@ -4139,19 +4139,19 @@
         <v>0.3428571428571427</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.09756895459317172</v>
+        <v>0.07444113308463218</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.07711991325867973</v>
+        <v>-0.02482578830356985</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.1746888678518514</v>
+        <v>0.09926692138820203</v>
       </c>
       <c r="AG26" t="n">
         <v>80</v>
       </c>
       <c r="AH26" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI26" t="b">
         <v>1</v>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>92.40000152587891</v>
       </c>
       <c r="R27" t="n">
-        <v>2509595</v>
+        <v>2458862</v>
       </c>
       <c r="S27" t="n">
         <v>91.56000213623047</v>
@@ -4258,16 +4258,16 @@
         <v>88.04166653951009</v>
       </c>
       <c r="W27" t="n">
-        <v>0.5871852951527643</v>
+        <v>0.5871852951527501</v>
       </c>
       <c r="X27" t="n">
-        <v>0.6438754215860085</v>
+        <v>0.6438754215859908</v>
       </c>
       <c r="Y27" t="n">
-        <v>-0.05669012643324423</v>
+        <v>-0.05669012643324067</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.1623141115072071</v>
+        <v>-0.1623141115072027</v>
       </c>
       <c r="AA27" t="b">
         <v>1</v>
@@ -4279,19 +4279,19 @@
         <v>0.1092436751588939</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.04628720978312884</v>
+        <v>-0.06941503129166837</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.3107333809569286</v>
+        <v>-0.2584392560018187</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.2644461711737998</v>
+        <v>0.1890242247101503</v>
       </c>
       <c r="AG27" t="n">
         <v>52</v>
       </c>
       <c r="AH27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI27" t="b">
         <v>1</v>
@@ -4383,7 +4383,7 @@
         <v>1380</v>
       </c>
       <c r="R28" t="n">
-        <v>1223811</v>
+        <v>1190191</v>
       </c>
       <c r="S28" t="n">
         <v>1319</v>
@@ -4401,13 +4401,13 @@
         <v>-11.68686481763621</v>
       </c>
       <c r="X28" t="n">
-        <v>-22.99993270421101</v>
+        <v>-22.99993270421102</v>
       </c>
       <c r="Y28" t="n">
         <v>11.31306788657481</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.510448522073439</v>
+        <v>3.510448522073442</v>
       </c>
       <c r="AA28" t="b">
         <v>1</v>
@@ -4419,13 +4419,13 @@
         <v>0.4330218068535825</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.151379280270556</v>
+        <v>-0.1745071017790956</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.01304475073776001</v>
+        <v>0.06533887569286989</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.164424031008316</v>
+        <v>-0.2398459774719655</v>
       </c>
       <c r="AG28" t="n">
         <v>22</v>
@@ -4523,7 +4523,7 @@
         <v>4390</v>
       </c>
       <c r="R29" t="n">
-        <v>12924532</v>
+        <v>12120210</v>
       </c>
       <c r="S29" t="n">
         <v>4412</v>
@@ -4559,13 +4559,13 @@
         <v>1.701538461538461</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.11340945212381</v>
+        <v>0.0902816306152705</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.281561405422639</v>
+        <v>1.333855530377749</v>
       </c>
       <c r="AF29" t="n">
-        <v>-1.168151953298829</v>
+        <v>-1.243573899762478</v>
       </c>
       <c r="AG29" t="n">
         <v>82</v>
@@ -4663,7 +4663,7 @@
         <v>968</v>
       </c>
       <c r="R30" t="n">
-        <v>20949029</v>
+        <v>20033869</v>
       </c>
       <c r="S30" t="n">
         <v>959.8</v>
@@ -4699,13 +4699,13 @@
         <v>0.939879759519038</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.05359700651754062</v>
+        <v>-0.07672482802608016</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.5199027034032155</v>
+        <v>0.5721968283583254</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.5734997099207562</v>
+        <v>-0.6489216563844056</v>
       </c>
       <c r="AG30" t="n">
         <v>50</v>
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>268.5</v>
       </c>
       <c r="R31" t="n">
-        <v>68426612</v>
+        <v>67328101</v>
       </c>
       <c r="S31" t="n">
         <v>267.5</v>
@@ -4821,13 +4821,13 @@
         <v>0.5493819255026438</v>
       </c>
       <c r="X31" t="n">
-        <v>3.295099460379339</v>
+        <v>3.295099460379334</v>
       </c>
       <c r="Y31" t="n">
-        <v>-2.745717534876695</v>
+        <v>-2.74571753487669</v>
       </c>
       <c r="Z31" t="n">
-        <v>-3.171731307869642</v>
+        <v>-3.171731307869636</v>
       </c>
       <c r="AA31" t="b">
         <v>1</v>
@@ -4839,19 +4839,19 @@
         <v>0.3698979591836735</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.03836178133756407</v>
+        <v>-0.06148960284610361</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.05007909693214896</v>
+        <v>0.002215028022960919</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.01171731559458489</v>
+        <v>-0.06370463086906453</v>
       </c>
       <c r="AG31" t="n">
         <v>60</v>
       </c>
       <c r="AH31" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI31" t="b">
         <v>0</v>
@@ -4943,7 +4943,7 @@
         <v>2150</v>
       </c>
       <c r="R32" t="n">
-        <v>11302188</v>
+        <v>10417286</v>
       </c>
       <c r="S32" t="n">
         <v>2185.0763671875</v>
@@ -4979,13 +4979,13 @@
         <v>0.5327960552223616</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.05855884178377746</v>
+        <v>-0.081686663292317</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.1128189991065391</v>
+        <v>0.165113124061649</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.1713778408903166</v>
+        <v>-0.246799787353966</v>
       </c>
       <c r="AG32" t="n">
         <v>46</v>
@@ -5083,7 +5083,7 @@
         <v>1355</v>
       </c>
       <c r="R33" t="n">
-        <v>3570805</v>
+        <v>3381867</v>
       </c>
       <c r="S33" t="n">
         <v>1342</v>
@@ -5101,13 +5101,13 @@
         <v>2.440208659738346</v>
       </c>
       <c r="X33" t="n">
-        <v>5.929656143604378</v>
+        <v>5.929656143604372</v>
       </c>
       <c r="Y33" t="n">
-        <v>-3.489447483866032</v>
+        <v>-3.489447483866027</v>
       </c>
       <c r="Z33" t="n">
-        <v>-3.936062255006854</v>
+        <v>-3.936062255006847</v>
       </c>
       <c r="AA33" t="b">
         <v>1</v>
@@ -5119,13 +5119,13 @@
         <v>0.4085239085239085</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.06873555801484277</v>
+        <v>-0.0918633795233823</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.01145314759191396</v>
+        <v>0.04084097736319592</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.05728241042292881</v>
+        <v>-0.1327043568865782</v>
       </c>
       <c r="AG33" t="n">
         <v>42</v>
@@ -5223,7 +5223,7 @@
         <v>6415</v>
       </c>
       <c r="R34" t="n">
-        <v>805729</v>
+        <v>757141</v>
       </c>
       <c r="S34" t="n">
         <v>6440</v>
@@ -5241,13 +5241,13 @@
         <v>184.0053761849395</v>
       </c>
       <c r="X34" t="n">
-        <v>143.7524475806851</v>
+        <v>143.752447580685</v>
       </c>
       <c r="Y34" t="n">
-        <v>40.25292860425435</v>
+        <v>40.25292860425441</v>
       </c>
       <c r="Z34" t="n">
-        <v>50.27142035210866</v>
+        <v>50.27142035210872</v>
       </c>
       <c r="AA34" t="b">
         <v>0</v>
@@ -5259,13 +5259,13 @@
         <v>0.7267833109017496</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.01218796390244647</v>
+        <v>-0.01093985760609306</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.3068062547859272</v>
+        <v>0.359100379741037</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.2946182908834807</v>
+        <v>-0.3700402373471301</v>
       </c>
       <c r="AG34" t="n">
         <v>64</v>
@@ -5365,7 +5365,7 @@
         <v>874</v>
       </c>
       <c r="R35" t="n">
-        <v>17726675</v>
+        <v>17183890</v>
       </c>
       <c r="S35" t="n">
         <v>868</v>
@@ -5383,13 +5383,13 @@
         <v>2.327944774039224</v>
       </c>
       <c r="X35" t="n">
-        <v>-0.4542524837273172</v>
+        <v>-0.454252483727319</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.782197257766541</v>
+        <v>2.782197257766543</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.850917262450268</v>
+        <v>2.85091726245027</v>
       </c>
       <c r="AA35" t="b">
         <v>0</v>
@@ -5401,13 +5401,13 @@
         <v>0.6367041198501873</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.1209166882043977</v>
+        <v>-0.1440445097129373</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.2167270637343648</v>
+        <v>0.2690211886894747</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.3376437519387625</v>
+        <v>-0.4130656984024119</v>
       </c>
       <c r="AG35" t="n">
         <v>32</v>
@@ -5507,7 +5507,7 @@
         <v>1365</v>
       </c>
       <c r="R36" t="n">
-        <v>1144164</v>
+        <v>1073522</v>
       </c>
       <c r="S36" t="n">
         <v>1393</v>
@@ -5525,13 +5525,13 @@
         <v>-1.027763504678887</v>
       </c>
       <c r="X36" t="n">
-        <v>15.91647903910819</v>
+        <v>15.91647903910818</v>
       </c>
       <c r="Y36" t="n">
-        <v>-16.94424254378708</v>
+        <v>-16.94424254378707</v>
       </c>
       <c r="Z36" t="n">
-        <v>-16.83967200218795</v>
+        <v>-16.83967200218794</v>
       </c>
       <c r="AA36" t="b">
         <v>0</v>
@@ -5543,13 +5543,13 @@
         <v>0.528555431131019</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.1007383560736894</v>
+        <v>-0.123866177582229</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.1085783750151965</v>
+        <v>0.1608724999703064</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.2093167310888859</v>
+        <v>-0.2847386775525353</v>
       </c>
       <c r="AG36" t="n">
         <v>36</v>
@@ -5647,7 +5647,7 @@
         <v>2435</v>
       </c>
       <c r="R37" t="n">
-        <v>4225506</v>
+        <v>4075666</v>
       </c>
       <c r="S37" t="n">
         <v>2443</v>
@@ -5665,13 +5665,13 @@
         <v>-0.7191208455669766</v>
       </c>
       <c r="X37" t="n">
-        <v>-1.195271527021309</v>
+        <v>-1.195271527021315</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.4761506814543319</v>
+        <v>0.4761506814543384</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.733790163070471</v>
+        <v>1.733790163070479</v>
       </c>
       <c r="AA37" t="b">
         <v>0</v>
@@ -5683,13 +5683,13 @@
         <v>0.5559105431309903</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.1413554274763716</v>
+        <v>-0.1644832489849112</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.1359334870151678</v>
+        <v>0.1882276119702777</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.2772889144915395</v>
+        <v>-0.3527108609551889</v>
       </c>
       <c r="AG37" t="n">
         <v>28</v>
@@ -5746,7 +5746,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>259.5</v>
       </c>
       <c r="R38" t="n">
-        <v>40413905</v>
+        <v>39425678</v>
       </c>
       <c r="S38" t="n">
         <v>258.6</v>
@@ -5805,13 +5805,13 @@
         <v>-1.254231640690193</v>
       </c>
       <c r="X38" t="n">
-        <v>0.365940243720115</v>
+        <v>0.3659402437200756</v>
       </c>
       <c r="Y38" t="n">
-        <v>-1.620171884410308</v>
+        <v>-1.620171884410269</v>
       </c>
       <c r="Z38" t="n">
-        <v>-1.921774657038597</v>
+        <v>-1.921774657038547</v>
       </c>
       <c r="AA38" t="b">
         <v>1</v>
@@ -5823,19 +5823,19 @@
         <v>0.2134372184757403</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.1073093964042247</v>
+        <v>-0.1304372179127642</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.2065398376400822</v>
+        <v>-0.1542457126849723</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.09923044123585756</v>
+        <v>0.02380849477220814</v>
       </c>
       <c r="AG38" t="n">
         <v>34</v>
       </c>
       <c r="AH38" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5927,7 +5927,7 @@
         <v>4860</v>
       </c>
       <c r="R39" t="n">
-        <v>4586160</v>
+        <v>4599361</v>
       </c>
       <c r="S39" t="n">
         <v>4810</v>
@@ -5945,13 +5945,13 @@
         <v>66.62470605580256</v>
       </c>
       <c r="X39" t="n">
-        <v>-22.60467905852392</v>
+        <v>-22.60467905852409</v>
       </c>
       <c r="Y39" t="n">
-        <v>89.22938511432648</v>
+        <v>89.22938511432665</v>
       </c>
       <c r="Z39" t="n">
-        <v>94.99208888265446</v>
+        <v>94.99208888265466</v>
       </c>
       <c r="AA39" t="b">
         <v>0</v>
@@ -5963,13 +5963,13 @@
         <v>0.8849966592579461</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.1593126539662668</v>
+        <v>-0.1824404754748064</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.4650196031421236</v>
+        <v>0.5173137280972335</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.6243322571083905</v>
+        <v>-0.6997542035720399</v>
       </c>
       <c r="AG39" t="n">
         <v>16</v>
@@ -6012,12 +6012,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -6039,11 +6039,11 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>436000</v>
+        <v>4334000</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -6052,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>436000</v>
+        <v>4334000</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -6061,87 +6061,85 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>9450</v>
+        <v>204.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>9450</v>
+        <v>204.5</v>
       </c>
       <c r="R40" t="n">
-        <v>193243</v>
+        <v>6051697</v>
       </c>
       <c r="S40" t="n">
-        <v>9672</v>
+        <v>209.1</v>
       </c>
       <c r="T40" t="n">
-        <v>8915.5</v>
+        <v>214.55</v>
       </c>
       <c r="U40" t="n">
-        <v>8918.5</v>
+        <v>215.475</v>
       </c>
       <c r="V40" t="n">
-        <v>9150.5</v>
+        <v>172.7033332824707</v>
       </c>
       <c r="W40" t="n">
-        <v>153.6259703940777</v>
+        <v>-1.089608366741174</v>
       </c>
       <c r="X40" t="n">
-        <v>-16.55327019416922</v>
+        <v>-0.3248805784357559</v>
       </c>
       <c r="Y40" t="n">
-        <v>170.179240588247</v>
+        <v>-0.7647277883054187</v>
       </c>
       <c r="Z40" t="n">
-        <v>210.5980821954069</v>
+        <v>-0.8522392626843568</v>
       </c>
       <c r="AA40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0.006309148264984188</v>
+        <v>-0.0829596412556054</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.1984781230183894</v>
+        <v>1.095286918003628</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.1295194144510332</v>
+        <v>-0.229297728950194</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.2214989330974331</v>
+        <v>0.7276039868429154</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.09197951864639986</v>
+        <v>-0.9569017157931093</v>
       </c>
       <c r="AG40" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AH40" t="n">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="AI40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="b">
         <v>0</v>
       </c>
       <c r="AK40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>213.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>8137.37</v>
+        <v>255.58</v>
       </c>
     </row>
     <row r="41">
@@ -6152,12 +6150,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6166,7 +6164,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>20.4</v>
+        <v>21</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6179,11 +6177,11 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4334000</v>
+        <v>436000</v>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -6192,7 +6190,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>4334000</v>
+        <v>436000</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -6201,85 +6199,87 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>204.5</v>
+        <v>9450</v>
       </c>
       <c r="Q41" t="n">
-        <v>204.5</v>
+        <v>9450</v>
       </c>
       <c r="R41" t="n">
-        <v>6136098</v>
+        <v>179690</v>
       </c>
       <c r="S41" t="n">
-        <v>209.1</v>
+        <v>9672</v>
       </c>
       <c r="T41" t="n">
-        <v>214.55</v>
+        <v>8915.5</v>
       </c>
       <c r="U41" t="n">
-        <v>215.475</v>
+        <v>8918.5</v>
       </c>
       <c r="V41" t="n">
-        <v>172.7033332824707</v>
+        <v>9150.5</v>
       </c>
       <c r="W41" t="n">
-        <v>-1.089608366741174</v>
+        <v>153.6259703940777</v>
       </c>
       <c r="X41" t="n">
-        <v>-0.3248805784357532</v>
+        <v>-16.55327019416922</v>
       </c>
       <c r="Y41" t="n">
-        <v>-0.7647277883054212</v>
+        <v>170.179240588247</v>
       </c>
       <c r="Z41" t="n">
-        <v>-0.85223926268436</v>
+        <v>210.5980821954069</v>
       </c>
       <c r="AA41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>-0.0829596412556054</v>
+        <v>-0.006309148264984188</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.095286918003628</v>
+        <v>0.1984781230183894</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.2061699074416544</v>
+        <v>-0.1526472359595727</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.6753098618878055</v>
+        <v>-0.1692048081423232</v>
       </c>
       <c r="AF41" t="n">
-        <v>-0.8814797693294599</v>
+        <v>0.01655757218275045</v>
       </c>
       <c r="AG41" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AH41" t="n">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="AI41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ41" t="b">
         <v>0</v>
       </c>
       <c r="AK41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>213.5</v>
+        <v>0</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP41" t="n">
-        <v>255.58</v>
+        <v>8137.37</v>
       </c>
     </row>
     <row r="42">
@@ -6304,7 +6304,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>2100</v>
       </c>
       <c r="R42" t="n">
-        <v>6988221</v>
+        <v>6861015</v>
       </c>
       <c r="S42" t="n">
         <v>2177</v>
@@ -6363,13 +6363,13 @@
         <v>-31.28261017471323</v>
       </c>
       <c r="X42" t="n">
-        <v>-32.07937754523451</v>
+        <v>-32.07937754523452</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.7967673705212803</v>
+        <v>0.7967673705212945</v>
       </c>
       <c r="Z42" t="n">
-        <v>5.65777884855499</v>
+        <v>5.657778848555004</v>
       </c>
       <c r="AA42" t="b">
         <v>0</v>
@@ -6381,19 +6381,19 @@
         <v>0.1864406779661016</v>
       </c>
       <c r="AD42" t="n">
-        <v>-0.1487323079493901</v>
+        <v>-0.1718601294579296</v>
       </c>
       <c r="AE42" t="n">
-        <v>-0.2335363781497208</v>
+        <v>-0.181242253194611</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.08480407020033076</v>
+        <v>0.009382123736681347</v>
       </c>
       <c r="AG42" t="n">
         <v>24</v>
       </c>
       <c r="AH42" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -6444,7 +6444,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>205</v>
       </c>
       <c r="R43" t="n">
-        <v>3952387</v>
+        <v>3865631</v>
       </c>
       <c r="S43" t="n">
         <v>201.2</v>
@@ -6503,13 +6503,13 @@
         <v>-3.328609751023265</v>
       </c>
       <c r="X43" t="n">
-        <v>-0.4639213831637019</v>
+        <v>-0.463921383163708</v>
       </c>
       <c r="Y43" t="n">
-        <v>-2.864688367859563</v>
+        <v>-2.864688367859557</v>
       </c>
       <c r="Z43" t="n">
-        <v>-3.796386410417729</v>
+        <v>-3.796386410417721</v>
       </c>
       <c r="AA43" t="b">
         <v>1</v>
@@ -6521,19 +6521,19 @@
         <v>0.004901960784313708</v>
       </c>
       <c r="AD43" t="n">
-        <v>-0.1446899797898676</v>
+        <v>-0.1678178012984072</v>
       </c>
       <c r="AE43" t="n">
-        <v>-0.4150750953315088</v>
+        <v>-0.3627809703763989</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.2703851155416411</v>
+        <v>0.1949631690779917</v>
       </c>
       <c r="AG43" t="n">
         <v>26</v>
       </c>
       <c r="AH43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6582,7 +6582,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>16.8</v>
+        <v>16.4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6595,11 +6595,11 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2492000</v>
+        <v>5191000</v>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -6608,7 +6608,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2492000</v>
+        <v>5191000</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -6617,61 +6617,61 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>5130</v>
+        <v>2400</v>
       </c>
       <c r="Q44" t="n">
-        <v>5130</v>
+        <v>2400</v>
       </c>
       <c r="R44" t="n">
-        <v>1744374</v>
+        <v>3136138</v>
       </c>
       <c r="S44" t="n">
-        <v>4968</v>
+        <v>2390</v>
       </c>
       <c r="T44" t="n">
-        <v>5254.25</v>
+        <v>2560</v>
       </c>
       <c r="U44" t="n">
-        <v>5265</v>
+        <v>2564.75</v>
       </c>
       <c r="V44" t="n">
-        <v>4642.25</v>
+        <v>2471.75</v>
       </c>
       <c r="W44" t="n">
-        <v>-62.95051576770402</v>
+        <v>-60.03117086725797</v>
       </c>
       <c r="X44" t="n">
-        <v>-23.40822264482729</v>
+        <v>-36.900279770715</v>
       </c>
       <c r="Y44" t="n">
-        <v>-39.54229312287673</v>
+        <v>-23.13089109654297</v>
       </c>
       <c r="Z44" t="n">
-        <v>-66.74669513574591</v>
+        <v>-32.40244644054764</v>
       </c>
       <c r="AA44" t="b">
         <v>1</v>
       </c>
       <c r="AB44" t="n">
-        <v>-0.04022450888681006</v>
+        <v>-0.03807615230460926</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.4074074074074074</v>
+        <v>0.2030075187969924</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.1634347750728591</v>
+        <v>-0.1844142399991978</v>
       </c>
       <c r="AE44" t="n">
-        <v>-0.01256964870841504</v>
+        <v>-0.1646754123637202</v>
       </c>
       <c r="AF44" t="n">
-        <v>-0.150865126364444</v>
+        <v>-0.01973882763547763</v>
       </c>
       <c r="AG44" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH44" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6692,10 +6692,10 @@
         <v>1</v>
       </c>
       <c r="AO44" t="n">
-        <v>5581.44</v>
+        <v>2664</v>
       </c>
       <c r="AP44" t="n">
-        <v>5655.79</v>
+        <v>2713.42</v>
       </c>
     </row>
     <row r="45">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6720,7 +6720,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>16.2</v>
+        <v>15.6</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6733,11 +6733,11 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5191000</v>
+        <v>1811000</v>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -6746,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>5191000</v>
+        <v>1811000</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -6755,61 +6755,61 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2400</v>
+        <v>1755</v>
       </c>
       <c r="Q45" t="n">
-        <v>2400</v>
+        <v>1755</v>
       </c>
       <c r="R45" t="n">
-        <v>3310976</v>
+        <v>814870</v>
       </c>
       <c r="S45" t="n">
-        <v>2390</v>
+        <v>1751</v>
       </c>
       <c r="T45" t="n">
-        <v>2560</v>
+        <v>1859.75</v>
       </c>
       <c r="U45" t="n">
-        <v>2564.75</v>
+        <v>1862.5</v>
       </c>
       <c r="V45" t="n">
-        <v>2471.75</v>
+        <v>1880</v>
       </c>
       <c r="W45" t="n">
-        <v>-60.03117086725797</v>
+        <v>-44.71998733086548</v>
       </c>
       <c r="X45" t="n">
-        <v>-36.90027977071497</v>
+        <v>-21.75812120273915</v>
       </c>
       <c r="Y45" t="n">
-        <v>-23.130891096543</v>
+        <v>-22.96186612812633</v>
       </c>
       <c r="Z45" t="n">
-        <v>-32.40244644054766</v>
+        <v>-30.00913363500874</v>
       </c>
       <c r="AA45" t="b">
         <v>1</v>
       </c>
       <c r="AB45" t="n">
-        <v>-0.03807615230460926</v>
+        <v>-0.03038674033149169</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.2030075187969924</v>
+        <v>-0.05898123324396787</v>
       </c>
       <c r="AD45" t="n">
-        <v>-0.1612864184906583</v>
+        <v>-0.1767248280260802</v>
       </c>
       <c r="AE45" t="n">
-        <v>-0.2169695373188301</v>
+        <v>-0.4266641644046805</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.05568311882817178</v>
+        <v>0.2499393363786002</v>
       </c>
       <c r="AG45" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AH45" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6830,10 +6830,10 @@
         <v>1</v>
       </c>
       <c r="AO45" t="n">
-        <v>2664</v>
+        <v>2014.74</v>
       </c>
       <c r="AP45" t="n">
-        <v>2713.42</v>
+        <v>1905.26</v>
       </c>
     </row>
     <row r="46">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6871,11 +6871,11 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1811000</v>
+        <v>1000</v>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -6884,7 +6884,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1811000</v>
+        <v>1000</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -6893,61 +6893,61 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1755</v>
+        <v>4380</v>
       </c>
       <c r="Q46" t="n">
-        <v>1755</v>
+        <v>4380</v>
       </c>
       <c r="R46" t="n">
-        <v>870216</v>
+        <v>2106090</v>
       </c>
       <c r="S46" t="n">
-        <v>1751</v>
+        <v>4274</v>
       </c>
       <c r="T46" t="n">
-        <v>1859.75</v>
+        <v>4409.5</v>
       </c>
       <c r="U46" t="n">
-        <v>1862.5</v>
+        <v>4435.75</v>
       </c>
       <c r="V46" t="n">
-        <v>1880</v>
+        <v>4024.083333333333</v>
       </c>
       <c r="W46" t="n">
-        <v>-44.71998733086548</v>
+        <v>-48.34781795552317</v>
       </c>
       <c r="X46" t="n">
-        <v>-21.75812120273914</v>
+        <v>-67.41448864829414</v>
       </c>
       <c r="Y46" t="n">
-        <v>-22.96186612812634</v>
+        <v>19.06667069277097</v>
       </c>
       <c r="Z46" t="n">
-        <v>-30.00913363500875</v>
+        <v>3.071073249297058</v>
       </c>
       <c r="AA46" t="b">
         <v>1</v>
       </c>
       <c r="AB46" t="n">
-        <v>-0.03038674033149169</v>
+        <v>-0.1070336391437309</v>
       </c>
       <c r="AC46" t="n">
-        <v>-0.05898123324396787</v>
+        <v>0.3730407523510972</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.1535970065175407</v>
+        <v>-0.2533717268383194</v>
       </c>
       <c r="AE46" t="n">
-        <v>-0.4789582893597903</v>
+        <v>0.005357821190384637</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.3253612828422496</v>
+        <v>-0.2587295480287041</v>
       </c>
       <c r="AG46" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AH46" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6956,22 +6956,24 @@
         <v>0</v>
       </c>
       <c r="AK46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM46" t="b">
         <v>1</v>
       </c>
       <c r="AN46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>2014.74</v>
+        <v>0</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP46" t="n">
-        <v>1905.26</v>
+        <v>4926.05</v>
       </c>
     </row>
     <row r="47">
@@ -6996,7 +6998,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -7037,7 +7039,7 @@
         <v>98.09999847412109</v>
       </c>
       <c r="R47" t="n">
-        <v>21638033</v>
+        <v>21501870</v>
       </c>
       <c r="S47" t="n">
         <v>95.83999938964844</v>
@@ -7055,13 +7057,13 @@
         <v>-2.410840006014226</v>
       </c>
       <c r="X47" t="n">
-        <v>-2.569171642122382</v>
+        <v>-2.569171642122389</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.1583316361081564</v>
+        <v>0.158331636108163</v>
       </c>
       <c r="Z47" t="n">
-        <v>-0.3521329216939746</v>
+        <v>-0.3521329216939666</v>
       </c>
       <c r="AA47" t="b">
         <v>1</v>
@@ -7073,19 +7075,19 @@
         <v>-0.05217392778626961</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.1567078181651516</v>
+        <v>-0.1798356396736911</v>
       </c>
       <c r="AE47" t="n">
-        <v>-0.4721509839020921</v>
+        <v>-0.4198568589469822</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.3154431657369405</v>
+        <v>0.2400212192732911</v>
       </c>
       <c r="AG47" t="n">
         <v>18</v>
       </c>
       <c r="AH47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -7122,12 +7124,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,11 +7151,11 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1000</v>
+        <v>1642000</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -7162,7 +7164,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1000</v>
+        <v>1642000</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -7171,61 +7173,61 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>4380</v>
+        <v>693</v>
       </c>
       <c r="Q48" t="n">
-        <v>4380</v>
+        <v>693</v>
       </c>
       <c r="R48" t="n">
-        <v>2254733</v>
+        <v>2336825</v>
       </c>
       <c r="S48" t="n">
-        <v>4274</v>
+        <v>675.6</v>
       </c>
       <c r="T48" t="n">
-        <v>4409.5</v>
+        <v>750.15</v>
       </c>
       <c r="U48" t="n">
-        <v>4435.75</v>
+        <v>754.95</v>
       </c>
       <c r="V48" t="n">
-        <v>4024.083333333333</v>
+        <v>645.1595260620118</v>
       </c>
       <c r="W48" t="n">
-        <v>-48.34781795552317</v>
+        <v>-22.29641314618584</v>
       </c>
       <c r="X48" t="n">
-        <v>-67.41448864829343</v>
+        <v>-15.37163681673735</v>
       </c>
       <c r="Y48" t="n">
-        <v>19.06667069277026</v>
+        <v>-6.924776329448491</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.071073249296177</v>
+        <v>-12.31809557517377</v>
       </c>
       <c r="AA48" t="b">
         <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>-0.1070336391437309</v>
+        <v>-0.1216730038022814</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.3730407523510972</v>
+        <v>0.4149313916455692</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.2302439053297799</v>
+        <v>-0.26801109149687</v>
       </c>
       <c r="AE48" t="n">
-        <v>-0.04693630376472524</v>
+        <v>0.04724846048485665</v>
       </c>
       <c r="AF48" t="n">
-        <v>-0.1833076015650547</v>
+        <v>-0.3152595519817266</v>
       </c>
       <c r="AG48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH48" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -7234,24 +7236,22 @@
         <v>0</v>
       </c>
       <c r="AK48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="b">
         <v>1</v>
       </c>
       <c r="AN48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>772</v>
       </c>
       <c r="AP48" t="n">
-        <v>4926.05</v>
+        <v>855.16</v>
       </c>
     </row>
     <row r="49">
@@ -7262,12 +7262,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7276,7 +7276,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7289,11 +7289,11 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1642000</v>
+        <v>852000</v>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -7302,7 +7302,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1642000</v>
+        <v>852000</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -7311,61 +7311,61 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>693</v>
+        <v>2290</v>
       </c>
       <c r="Q49" t="n">
-        <v>693</v>
+        <v>2290</v>
       </c>
       <c r="R49" t="n">
-        <v>2412282</v>
+        <v>1055612</v>
       </c>
       <c r="S49" t="n">
-        <v>675.6</v>
+        <v>2285</v>
       </c>
       <c r="T49" t="n">
-        <v>750.15</v>
+        <v>2426.75</v>
       </c>
       <c r="U49" t="n">
-        <v>754.95</v>
+        <v>2438.5</v>
       </c>
       <c r="V49" t="n">
-        <v>645.1595260620118</v>
+        <v>2429.583333333333</v>
       </c>
       <c r="W49" t="n">
-        <v>-22.29641314618561</v>
+        <v>-59.8052702818286</v>
       </c>
       <c r="X49" t="n">
-        <v>-15.37163681673713</v>
+        <v>-61.02414486816085</v>
       </c>
       <c r="Y49" t="n">
-        <v>-6.924776329448481</v>
+        <v>1.218874586332255</v>
       </c>
       <c r="Z49" t="n">
-        <v>-12.31809557517376</v>
+        <v>-4.526472139308936</v>
       </c>
       <c r="AA49" t="b">
         <v>1</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.1216730038022814</v>
+        <v>-0.09306930693069304</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.4149313916455692</v>
+        <v>0.1536523929471032</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.2448832699883304</v>
+        <v>-0.2394073946252816</v>
       </c>
       <c r="AE49" t="n">
-        <v>-0.005045664470253231</v>
+        <v>-0.2140305382136094</v>
       </c>
       <c r="AF49" t="n">
-        <v>-0.2398376055180772</v>
+        <v>-0.0253768564116722</v>
       </c>
       <c r="AG49" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AH49" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -7374,22 +7374,24 @@
         <v>0</v>
       </c>
       <c r="AK49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM49" t="b">
         <v>1</v>
       </c>
       <c r="AN49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>772</v>
+        <v>0</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Already &gt; 0</t>
+        </is>
       </c>
       <c r="AP49" t="n">
-        <v>855.16</v>
+        <v>2698.95</v>
       </c>
     </row>
     <row r="50">
@@ -7400,12 +7402,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7414,7 +7416,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7427,11 +7429,11 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>852000</v>
+        <v>3528000</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -7440,7 +7442,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>852000</v>
+        <v>3528000</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -7449,61 +7451,61 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2290</v>
+        <v>332.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>2290</v>
+        <v>332.5</v>
       </c>
       <c r="R50" t="n">
-        <v>1086719</v>
+        <v>2278374</v>
       </c>
       <c r="S50" t="n">
-        <v>2285</v>
+        <v>327.5</v>
       </c>
       <c r="T50" t="n">
-        <v>2426.75</v>
+        <v>360.85</v>
       </c>
       <c r="U50" t="n">
-        <v>2438.5</v>
+        <v>363.05</v>
       </c>
       <c r="V50" t="n">
-        <v>2429.583333333333</v>
+        <v>361.4916666666667</v>
       </c>
       <c r="W50" t="n">
-        <v>-59.8052702818286</v>
+        <v>-13.25898126111616</v>
       </c>
       <c r="X50" t="n">
-        <v>-61.02414486816082</v>
+        <v>-10.29216635378428</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.21887458633222</v>
+        <v>-2.966814907331884</v>
       </c>
       <c r="Z50" t="n">
-        <v>-4.526472139308979</v>
+        <v>-4.620011422980134</v>
       </c>
       <c r="AA50" t="b">
         <v>1</v>
       </c>
       <c r="AB50" t="n">
-        <v>-0.09306930693069304</v>
+        <v>-0.1168658698539177</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.1536523929471032</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AD50" t="n">
-        <v>-0.2162795731167421</v>
+        <v>-0.2632039575485062</v>
       </c>
       <c r="AE50" t="n">
-        <v>-0.2663246631687193</v>
+        <v>-0.2010162644940459</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.05004509005197721</v>
+        <v>-0.06218769305446037</v>
       </c>
       <c r="AG50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH50" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -7512,24 +7514,22 @@
         <v>0</v>
       </c>
       <c r="AK50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="b">
         <v>1</v>
       </c>
       <c r="AN50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Already &gt; 0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>366.42</v>
       </c>
       <c r="AP50" t="n">
-        <v>2698.95</v>
+        <v>417.34</v>
       </c>
     </row>
     <row r="51">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7554,7 +7554,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>12.6</v>
+        <v>10</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7567,11 +7567,11 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>3528000</v>
+        <v>2492000</v>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -7580,7 +7580,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3528000</v>
+        <v>2492000</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -7589,61 +7589,61 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>332.5</v>
+        <v>1710</v>
       </c>
       <c r="Q51" t="n">
-        <v>332.5</v>
+        <v>1710</v>
       </c>
       <c r="R51" t="n">
-        <v>2347073</v>
+        <v>4638384</v>
       </c>
       <c r="S51" t="n">
-        <v>327.5</v>
+        <v>1656</v>
       </c>
       <c r="T51" t="n">
-        <v>360.85</v>
+        <v>4094.083337402344</v>
       </c>
       <c r="U51" t="n">
-        <v>363.05</v>
+        <v>4275.833337402344</v>
       </c>
       <c r="V51" t="n">
-        <v>361.4916666666667</v>
+        <v>4255.527779134115</v>
       </c>
       <c r="W51" t="n">
-        <v>-13.25898126111616</v>
+        <v>-957.086643197239</v>
       </c>
       <c r="X51" t="n">
-        <v>-10.29216635378428</v>
+        <v>-667.4761941077724</v>
       </c>
       <c r="Y51" t="n">
-        <v>-2.966814907331884</v>
+        <v>-289.6104490894667</v>
       </c>
       <c r="Z51" t="n">
-        <v>-4.620011422980136</v>
+        <v>-385.0157962544139</v>
       </c>
       <c r="AA51" t="b">
         <v>1</v>
       </c>
       <c r="AB51" t="n">
-        <v>-0.1168658698539177</v>
+        <v>-0.6800748362956034</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.1666666666666667</v>
+        <v>-0.5308641975308642</v>
       </c>
       <c r="AD51" t="n">
-        <v>-0.2400761360399667</v>
+        <v>-0.8264129239901919</v>
       </c>
       <c r="AE51" t="n">
-        <v>-0.2533103894491557</v>
+        <v>-0.8985471286915768</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.01323425340918905</v>
+        <v>0.07213420470138487</v>
       </c>
       <c r="AG51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="AI51" t="b">
         <v>0</v>
@@ -7661,13 +7661,11 @@
         <v>1</v>
       </c>
       <c r="AN51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>366.42</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AO51" t="inlineStr"/>
       <c r="AP51" t="n">
-        <v>417.34</v>
+        <v>8034.56</v>
       </c>
     </row>
   </sheetData>
